--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_891_Montenegro.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_891_Montenegro.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rcc343f43fee04f4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Ra59316f0fc8b4d6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf9efd0c451d24988"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rff46372d52d14d5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R2534a97511cf4046"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R6d9285d125d4438e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R729f8319214243bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R951bedf45c8f4807"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rcd7721d5ddf7458a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rf81af3f6ce7d4e42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R69402c89eecb4732"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R80ec34136bf74a1b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ891CommercialTable" displayName="EEZ891CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ891CommercialTable" displayName="EEZ891CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ891FunctionalTable" displayName="EEZ891FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ891FunctionalTable" displayName="EEZ891FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ891ValidationTable" displayName="EEZ891ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ891ValidationTable" displayName="EEZ891ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5384,7 +5338,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb07a88f26ca0497d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra291e3fe2c354ae9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5394,20 +5348,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5415,606 +5359,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>287.38751886299997</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.141332379616641</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>138.46256723847156</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>287.38751886299997</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>139.1522342397631</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$71,A2,'Species'!$U$2:$U$71))</x:f>
-        <x:v>39990.615342408506</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.141332379616641</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>138.46256723847156</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>39792.41365406565</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>198.2016883428587</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0049808913343614</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.004980891334361371</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>64.16498647</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.221872486113063</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>166.6757761328508</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>64.16498647</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>185.17947462866354</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$71,A3,'Species'!$U$2:$U$71))</x:f>
-        <x:v>11882.038484069904</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.221872486113063</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>166.6757761328508</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>10694.748920441121</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1187.289563628783</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1110161231891558</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.11101612318915585</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>38.575259802000005</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.547280835917674</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>352.5988048606859</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>38.575259802000005</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>359.0785562225289</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$71,A4,'Species'!$U$2:$U$71))</x:f>
-        <x:v>13851.548595611119</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.547280835917674</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>352.5988048606859</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>13601.59050337566</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>249.95809223545803</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0183771223059115</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.018377122305911438</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>543.6242589100001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.114212667507704</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>130.08064075262297</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>543.6242589100001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>132.92485874750463</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$71,A5,'Species'!$U$2:$U$71))</x:f>
-        <x:v>72261.17782732865</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.114212667507704</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>130.08064075262297</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>70714.99192768261</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1546.185899646036</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0218650367835331</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.021865036783533232</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>58.560043115</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.076742509987136</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>11.932804074896852</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>58.560043115</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>11.98705860005372</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$71,A6,'Species'!$U$2:$U$71))</x:f>
-        <x:v>701.9626684411774</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.076742509987136</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>11.932804074896852</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>698.7855211088073</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>3.1771473323700548</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.004546670239144</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.00454667023914387</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>372.99474812159997</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.4495707278710226</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>281.5598517560129</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>372.99474812159997</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>467.4972161320179</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$71,A7,'Species'!$U$2:$U$71))</x:f>
-        <x:v>174374.0063787112</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.4495707278710226</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>281.5598517560129</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>105020.34598688906</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>69353.66039182214</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.6603830880587689</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.6603830880587689</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>270.8322542662</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3959071306623163</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>248.8325159047471</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>270.8322542662</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>571.8905289615037</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$71,A8,'Species'!$U$2:$U$71))</x:f>
-        <x:v>154886.4011521336</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3959071306623163</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>248.8325159047471</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>67391.87121721273</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>87494.52993492087</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>2.298295007314972</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>1.2982950073149722</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>7.30774233</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.915963199791693</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>824.0682841248466</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>7.30774233</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>827.4321279486439</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$71,A9,'Species'!$U$2:$U$71))</x:f>
-        <x:v>6046.660786612281</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.915963199791693</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>824.0682841248466</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>6022.078682709609</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>24.582103902672316</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.004081996466312</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.004081996466311812</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>24.677918758</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.6113221812361886</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>408.6224103369585</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>24.677918758</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>453.91584597513776</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$71,A10,'Species'!$U$2:$U$71))</x:f>
-        <x:v>11201.698369943291</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.6113221812361886</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>408.6224103369585</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>10083.950644993602</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1117.7477249496897</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1108442280510982</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.11084422805109821</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>29.887132381299995</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.475407815751809</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2988.1873007989116</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>29.887132381299995</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>3026.9961060087608</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$71,A11,'Species'!$U$2:$U$71))</x:f>
-        <x:v>90468.23333796342</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.475407815751809</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2988.1873007989116</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>89308.34943909658</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1159.883898866843</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0129874071814284</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.012987407181428436</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05b7c6ed61044cbd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7f46aef5339447a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6024,20 +5574,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6045,1146 +5585,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>57.96297612699999</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.7599082002254627</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>575.3183155434548</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>57.96297612699999</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>596.6961107825723</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$71,A2,'Species'!$U$2:$U$71))</x:f>
-        <x:v>34586.28242436398</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.7599082002254627</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>575.3183155434548</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>33347.161789271115</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1239.1206350928624</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.037158203835252</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.037158203835251986</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>31.557038376199998</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.6006183031777383</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>39.86743576675146</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>31.557038376199998</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>664.1887379800766</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$71,A3,'Species'!$U$2:$U$71))</x:f>
-        <x:v>20959.829493477122</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.6006183031777383</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>39.86743576675146</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1258.0982004520642</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>19701.73129302506</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>16.65993122472138</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>15.65993122472138</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>7.840549234</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.201229002720653</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1589.3846074010032</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>7.840549234</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1800.3057522619124</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$71,A4,'Species'!$U$2:$U$71))</x:f>
-        <x:v>14115.38588686293</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.201229002720653</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1589.3846074010032</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>12461.648266089327</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1653.7376207736033</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1327061706013448</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.13270617060134485</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>4.1651307463</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.42402060045483</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2654.7314843191775</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>4.1651307463</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2667.636299952279</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$71,A5,'Species'!$U$2:$U$71))</x:f>
-        <x:v>11111.053972877206</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.42402060045483</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2654.7314843191775</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>11057.303728508443</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>53.75024436876265</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.00486106248761</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.004861062487610006</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>6.838959379</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.5369275021161077</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>344.29245235007437</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>6.838959379</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>390.48294598827164</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$71,A6,'Species'!$U$2:$U$71))</x:f>
-        <x:v>2670.4970058060408</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.5369275021161077</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>344.29245235007437</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2354.6020961184518</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>315.894909687589</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1341606338533121</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.1341606338533122</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>17.964032721000002</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.29834928373709</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1987.6928876724037</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>17.964032721000002</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2352.0193929429315</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$71,A7,'Species'!$U$2:$U$71))</x:f>
-        <x:v>42251.75333525339</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.29834928373709</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1987.6928876724037</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>35706.980073446044</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>6544.773261807342</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1832911449902885</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.18329114499028853</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>7.838959379</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.818237911048882</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>658.0182078794842</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>7.838959379</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>684.9026056126565</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$71,A8,'Species'!$U$2:$U$71))</x:f>
-        <x:v>5368.923703968872</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.818237911048882</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>658.0182078794842</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>5158.178002209655</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>210.7457017592178</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0408566167489641</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.04085661674896423</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>15.241463312999999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.0680016772816017</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>116.95039077330262</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>15.241463312999999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>171.278303722991</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$71,A9,'Species'!$U$2:$U$71))</x:f>
-        <x:v>2610.5319825068386</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.0680016772816017</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>116.95039077330262</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1782.4950904123054</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>828.0368920945332</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.464538105349284</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.4645381053492841</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>16.999999997</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.46</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2884.031503126606</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>16.999999997</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2884.031503126606</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$71,A10,'Species'!$U$2:$U$71))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>49028.535544500206</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.46</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2884.031503126606</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>49028.535544500206</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>32.925279934</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.5651926638295173</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>367.44527220436436</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>32.925279934</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>889.297916478202</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$71,A11,'Species'!$U$2:$U$71))</x:f>
-        <x:v>29280.38284476775</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.5651926638295173</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>367.44527220436436</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>12098.238447753527</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>17182.144397014225</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>2.4202186930945064</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>1.4202186930945064</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>333.5775742515</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.2347412846747083</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>171.6885309753482</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>333.5775742515</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>188.97141396751468</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$71,A12,'Species'!$U$2:$U$71))</x:f>
-        <x:v>63036.62587415957</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.2347412846747083</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>171.6885309753482</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>57271.44368956016</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>5765.182184599405</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1006641672217934</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.10066416722179335</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>109.30549618210001</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.9617965853870944</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>915.7914517520569</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>109.30549618210001</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1295.696915713182</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$71,A13,'Species'!$U$2:$U$71))</x:f>
-        <x:v>141626.794273646</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.9617965853870944</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>915.7914517520569</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>100101.03903308428</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>41525.75524056172</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.4148384036936628</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.4148384036936628</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>52.06419459299999</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.468353716148689</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>294.00432292009447</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>52.06419459299999</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>318.7722102241336</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$71,A14,'Species'!$U$2:$U$71))</x:f>
-        <x:v>16596.61838394999</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.468353716148689</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>294.00432292009447</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>15307.098279695005</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>1289.5201042549852</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0842432759424785</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.08424327594247856</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>58.560043115</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.076742509987136</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>11.932804074896852</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>58.560043115</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>11.98705860005372</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$71,A15,'Species'!$U$2:$U$71))</x:f>
-        <x:v>701.9626684411774</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.076742509987136</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>11.932804074896852</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>698.7855211088073</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>3.1771473323700548</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.004546670239144</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.00454667023914387</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>48.923523157</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.269808859792047</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>186.12677815345916</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>48.923523157</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>189.51019679858226</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$71,A16,'Species'!$U$2:$U$71))</x:f>
-        <x:v>9271.506501563066</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.269808859792047</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>186.12677815345916</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>9105.97774112856</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>165.5287604345067</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.018178032622117</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.018178032622117053</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>1.899153223</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.38</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>239.88329190194898</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>1.899153223</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$71,A17,'Species'!$U$2:$U$71))</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>455.5751269594362</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.38</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
-        <x:v>455.5751269594362</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>1.7460099960000002</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.58</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>380.1893963205613</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>1.7460099960000002</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>380.1893963205613</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$71,A18,'Species'!$U$2:$U$71))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>663.8144863489057</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.58</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>380.1893963205613</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>663.8144863489057</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>844.026219491</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.124769615631311</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>133.28142138290988</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>844.026219491</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>135.43944552685798</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$71,A19,'Species'!$U$2:$U$71))</x:f>
-        <x:v>114314.44317799117</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.124769615631311</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>133.28142138290988</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>112493.01421820436</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>1821.4289597868046</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.016191485066386</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.016191485066386006</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>38.575259802000005</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.547280835917674</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>352.5988048606859</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>38.575259802000005</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>359.0785562225289</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$71,A20,'Species'!$U$2:$U$71))</x:f>
-        <x:v>13851.548595611119</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.547280835917674</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>352.5988048606859</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>13601.59050337566</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>249.95809223545803</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0183771223059115</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.018377122305911438</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>316.22776601683796</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$71,A21,'Species'!$U$2:$U$71))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>3162.2776601683795</x:v>
       </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.5</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4b05f83e4bc41b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1c97afa151640b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7359,7 +6155,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -7458,7 +6254,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>575664.3429432232</x:v>
+        <x:v>413329.1264975754</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7472,7 +6268,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>575664.3429432232</x:v>
+        <x:v>477113.8574983947</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7486,7 +6282,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-162335.21644564782</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7500,7 +6296,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-98550.48544482852</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7511,9 +6307,9 @@
         <x:v>EEZ_891</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -7525,47 +6321,19 @@
         <x:v>EEZ_891</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_891</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_891</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86c1c7e1d8e5441d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4eadd66efcd1425c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7612,7 +6380,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
